--- a/data/outlier_test.xlsx
+++ b/data/outlier_test.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MONSTER\OneDrive - bandirma.edu.tr\Belgeler\GenericDataAnalyzer\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bandirmaedutr-my.sharepoint.com/personal/esrasilahsor_ogr_bandirma_edu_tr/Documents/Belgeler/GenericDataAnalyzer/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4874957-FA31-479C-A7D9-7DEEC9F33908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{D4874957-FA31-479C-A7D9-7DEEC9F33908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DA8460B-4332-4177-B55E-D8AB2FC4EEEA}"/>
   <bookViews>
     <workbookView xWindow="15" yWindow="2595" windowWidth="12360" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -391,7 +391,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>3</v>
@@ -424,7 +424,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>214</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>3</v>
@@ -446,7 +446,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>3</v>
@@ -468,7 +468,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>18</v>
+        <v>188</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>3</v>
